--- a/docs/controlcalidadpostcampo.xlsx
+++ b/docs/controlcalidadpostcampo.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brandon.mata\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EDD44CA-6987-4434-A967-3913C87E52A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BF8721-0268-4C30-80E5-A10CD54C381A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8304" xr2:uid="{4C214464-FD86-4D11-A2C3-1C6588017889}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" xr2:uid="{4C214464-FD86-4D11-A2C3-1C6588017889}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
-    <sheet name="Parametros" sheetId="3" r:id="rId2"/>
-    <sheet name="Ejemplo" sheetId="4" r:id="rId3"/>
+    <sheet name="Ejemplo" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,52 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
-  <si>
-    <t>Inspección Horas Extras</t>
-  </si>
-  <si>
-    <t>Atributos incompletos/erroneos</t>
-  </si>
-  <si>
-    <t>Autoensamblado</t>
-  </si>
-  <si>
-    <t>Diferencia de áreas</t>
-  </si>
-  <si>
-    <t>Errores gráficos</t>
-  </si>
-  <si>
-    <t>Puertas no coinciden</t>
-  </si>
-  <si>
-    <t>Recapitulación errónea</t>
-  </si>
-  <si>
-    <t>tipos de errores</t>
-  </si>
-  <si>
-    <t>distrito</t>
-  </si>
-  <si>
-    <t>manzana</t>
-  </si>
-  <si>
-    <t>sector</t>
-  </si>
-  <si>
-    <t>numero_lote</t>
-  </si>
-  <si>
-    <t>operador</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>tipo_de_errores</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>aprobados</t>
   </si>
@@ -80,77 +34,23 @@
     <t>rechazados</t>
   </si>
   <si>
-    <t>horas</t>
+    <t>15010821057019010101012</t>
   </si>
   <si>
-    <t>distritos</t>
+    <t>crc</t>
   </si>
   <si>
-    <t>Chorrillos</t>
+    <t>15010821057019010101013</t>
   </si>
   <si>
-    <t>Villa el Salvador</t>
-  </si>
-  <si>
-    <t>Inspección</t>
-  </si>
-  <si>
-    <t>Inspección Reproceso</t>
-  </si>
-  <si>
-    <t>Primera Reinspección</t>
-  </si>
-  <si>
-    <t>Control de Calidad Supervisión</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>001,002</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Ale</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>3,6</t>
-  </si>
-  <si>
-    <t>numero de error</t>
-  </si>
-  <si>
-    <t>San Juan De Miraflores</t>
+    <t>15010821057019010101014</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,26 +58,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -207,12 +94,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,303 +413,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F53408-ED47-4239-880B-41F7F35C723D}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="11.5546875" style="4"/>
-    <col min="6" max="6" width="20.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.88671875" style="4" customWidth="1"/>
-    <col min="8" max="10" width="11.5546875" style="4"/>
+    <col min="1" max="1" width="32.21875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="24.21875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>17</v>
-      </c>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
     </row>
   </sheetData>
-  <dataValidations xWindow="836" yWindow="420" count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Sin espacios,separado por coma:" prompt="1,2,3_x000a_1_x000a_3,6" sqref="G2:G1048576" xr:uid="{9B1FDB1B-E168-4C33-B51B-EE6B34A1BD82}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Formato:" prompt="Todos_x000a_1_x000a_1,3,5" sqref="D2:D1048576" xr:uid="{72A72E99-C694-4136-A878-42DA94647B3A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Nota:" prompt="puede poner el nombre o numero pero se debe seleccionar directamente en streamlit" sqref="E2:E1048576" xr:uid="{3C8E79E5-F51A-4837-9579-034E4A37CC65}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Formato" prompt="2.5 _x000a_solucion:_x000a_ctrl+b reemplazar , por ." sqref="J2:J1048576" xr:uid="{46F32BAF-FC21-416A-BCA9-20D67E640389}"/>
+  <dataValidations xWindow="836" yWindow="420" count="5">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="verifique tenga 23 digitos" promptTitle="CRC" prompt="23 digitos_x000a_" sqref="A2:A6" xr:uid="{5C2827CF-647B-436D-911E-D827E9FFF16C}">
+      <formula1>23</formula1>
+      <formula2>24</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B3:B1048576" xr:uid="{D2E11CD4-D009-425F-BB69-807641B10012}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numero no valido" error="Solo se admite 0 o 1" sqref="B2" xr:uid="{B73BEA0A-6369-4235-802D-74E906971DA6}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numero no valido" error="solo se admite 0 o 1" sqref="C1:C1048576" xr:uid="{54984F1F-F9CD-4142-AD21-FC539EE2BA46}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Debe elegir solo uno de los 3 distritos" sqref="A7:A1048576" xr:uid="{4C21E025-E712-4E2C-B193-E448B6018209}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="836" yWindow="420" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Debe elegir solo uno de los 3 distritos" xr:uid="{4C21E025-E712-4E2C-B193-E448B6018209}">
-          <x14:formula1>
-            <xm:f>Parametros!$C$2:$C$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error:" error="Solo puede elegir un valor de la lista" xr:uid="{A1A66D2C-A194-418D-A84E-E6195C9D59EB}">
-          <x14:formula1>
-            <xm:f>Parametros!$D$2:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8677D8F7-2869-4AB5-B09B-10DAAC86A5AC}">
-  <dimension ref="A1:D7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A1C3BF-9926-42E2-8809-77E52927C46F}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.77734375" customWidth="1"/>
-    <col min="3" max="4" width="22" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="C2" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
+      <c r="C4" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B1048576" xr:uid="{D268DF24-30C7-4AA8-873D-C4E22617529D}">
+      <formula1>0</formula1>
+      <formula2>9.99999999999999E+22</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numero no valido" error="solo se admite 0 o 1" sqref="C1:C4" xr:uid="{C9714814-042E-49A9-B186-9BA1B948912B}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Numero no valido" error="Solo se admite 0 o 1" sqref="B2" xr:uid="{A6C2FA4A-DF81-482F-84D5-B3FF438A339E}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 B3:B4" xr:uid="{E8E46780-8CA0-4F0D-92EC-C9A1D6D8E570}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="verifique tenga 23 digitos" promptTitle="CRC" prompt="23 digitos_x000a_" sqref="A2:A4" xr:uid="{3A0F2CDB-C80F-4D06-A245-3DAA080DFA1F}">
+      <formula1>23</formula1>
+      <formula2>24</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A1C3BF-9926-42E2-8809-77E52927C46F}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Formato" prompt="2.5 _x000a_solucion:_x000a_ctrl+b reemplazar , por ." sqref="J2:J3" xr:uid="{A4BF6054-BA3A-4C78-A14A-DFFA9971270A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Nota:" prompt="puede poner el nombre o numero pero se debe seleccionar directamente en streamlit" sqref="E2:E3" xr:uid="{48316D4C-BBBC-47AC-A182-4EB3CA3D6F8B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Formato:" prompt="Todos_x000a_1_x000a_1,3,5" sqref="D2:D3" xr:uid="{9C25E3BC-E63C-445A-AF47-7CB8E19AAABC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Sin espacios,separado por coma:" prompt="1,2,3_x000a_1_x000a_3,6" sqref="G2:G3" xr:uid="{AC80A569-A37E-4D3C-85AC-2B5D9D1FF5F8}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error:" error="Solo puede elegir un valor de la lista" xr:uid="{AB4E8360-41E0-4AF2-8614-C9BCAA30CF1B}">
-          <x14:formula1>
-            <xm:f>Parametros!$D$2:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Debe elegir solo uno de los 3 distritos" xr:uid="{86694846-0F35-46D6-AADA-635DCB06B801}">
-          <x14:formula1>
-            <xm:f>Parametros!$C$2:$C$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>A2:A3</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
 </file>